--- a/database/Event.xlsx
+++ b/database/Event.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Postgradute\Group7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Postgradute\Group7\Upthrift_Programming_Group-7\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B120DA09-7EC5-43DC-887A-582091F90011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A938E31E-FA02-4B4F-8C14-34AE5BED1B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>event_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -373,6 +373,18 @@
   </si>
   <si>
     <t>https://cdn.prod.website-files.com/63e253c521408834eddc954c/649f52de859ad52b57ebb4de_pexels-mart-production-7679438%20copy.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>existence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>real event</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fake event</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -732,424 +744,458 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="31.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.4140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.08203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.9140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.9140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="15" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.58203125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="8.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.4140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.08203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.9140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.9140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.58203125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="392" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:13" ht="392" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>53.342966974365702</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>-6.2594363177322396</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46166</v>
       </c>
       <c r="J2" s="3">
         <v>46166</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3">
+        <v>46166</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="392" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:13" ht="392" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>53.338803092262197</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>-6.2488870624686799</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46151</v>
       </c>
       <c r="I3" s="3">
         <v>46151</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="3">
+        <v>46151</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="285" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:13" ht="285" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>53.3457473614611</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>-6.2611994888966702</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>46122</v>
       </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <v>46124</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="98" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:13" ht="98" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>53.349607019992099</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>-6.28972995738458</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46124</v>
       </c>
       <c r="I5" s="3">
         <v>46124</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="3">
+        <v>46124</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="154" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:13" ht="154" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>53.341200000000001</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>-6.2758000000000003</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>46130</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>46131</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="70" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:13" ht="154" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>53.331499999999998</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>-6.2290999999999999</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46131</v>
       </c>
       <c r="I7" s="3">
         <v>46131</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="3">
+        <v>46131</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="70" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="1:13" ht="154" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>53.340499999999999</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>-6.2682000000000002</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>46133</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>46135</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="70" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:13" ht="154" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>53.3431</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>-6.2845000000000004</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46138</v>
       </c>
       <c r="I9" s="3">
         <v>46138</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="3">
+        <v>46138</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="70" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+    <row r="10" spans="1:13" ht="154" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>53.341799999999999</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>-6.2793999999999999</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46139</v>
       </c>
       <c r="I10" s="3">
         <v>46139</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="3">
+        <v>46139</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="70" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:13" ht="154" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>53.343800000000002</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>-6.2404999999999999</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>46142</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="3">
         <v>46143</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" display="https://www.eventbrite.ie/e/the-dublin-city-market-day-free-ticket-tickets-1987382068265?utm_experiment=test_share_listing&amp;aff=ebdsshios&amp;utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAdGRleAROHBZleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA8xMjQwMjQ1NzQyODc0MTQAAae215-Yd-tqIFjbtXD_cUQT-4ccnrwqhSa4VhMIkBsaqlwQgYTxCjGrsmhrqg_aem_q3vfFqtT5Qm7CSto3yc7oA&amp;utm_id=97760_v0_s00_e0_tv3_a1denngz84ieda" xr:uid="{CF6F10C5-539E-49AA-83C8-AD9F39D80343}"/>
-    <hyperlink ref="L2" r:id="rId2" display="https://www.eventbrite.ie/e/_next/image?url=https%3A%2F%2Fimg.evbuc.com%2Fhttps%253A%252F%252Fcdn.evbuc.com%252Fimages%252F1182114598%252F2661084054671%252F1%252Foriginal.20260414-091433%3Fcrop%3Dfocalpoint%26fit%3Dcrop%26w%3D1880%26auto%3Dformat%252Ccompress%26q%3D75%26sharp%3D10%26fp-x%3D0.035%26fp-y%3D0.057%26s%3D99e443b6a1e707f2900fc8362638f8de&amp;w=1880&amp;q=75" xr:uid="{776602D2-A3ED-4967-B8DD-852A6E4B2EE5}"/>
-    <hyperlink ref="K3" r:id="rId3" location="location" xr:uid="{DFF3B79C-DF6D-437C-B16D-D0F1CC8C4202}"/>
-    <hyperlink ref="L3" r:id="rId4" display="https://www.eventbrite.ie/e/_next/image?url=https%3A%2F%2Fimg.evbuc.com%2Fhttps%253A%252F%252Fcdn.evbuc.com%252Fimages%252F1180032649%252F168066979823%252F1%252Foriginal.20260317-114958%3Fcrop%3Dfocalpoint%26fit%3Dcrop%26w%3D1880%26auto%3Dformat%252Ccompress%26q%3D75%26sharp%3D10%26fp-x%3D0.412%26fp-y%3D0.492%26s%3D9d6a3ea730dd98c09ab63fedc0eaecf0&amp;w=1880&amp;q=75" xr:uid="{DEFF551F-E1BC-42F2-9D66-7AC8002FE594}"/>
-    <hyperlink ref="K4" r:id="rId5" xr:uid="{6DC4ED09-3686-471C-ABAC-9B6741F9B9E9}"/>
-    <hyperlink ref="L4" r:id="rId6" xr:uid="{9EFC1056-2A16-4651-8620-1706CCD6D391}"/>
-    <hyperlink ref="K5" r:id="rId7" xr:uid="{C4A85081-A2C8-45B9-AE33-65E55A0F9A84}"/>
-    <hyperlink ref="L5" r:id="rId8" xr:uid="{3C0F9B81-1FA4-4C70-87B7-49EA34BFC97B}"/>
-    <hyperlink ref="L6" r:id="rId9" xr:uid="{B7E078E3-DBC7-4446-912E-68BF23CFBE38}"/>
+    <hyperlink ref="L2" r:id="rId1" display="https://www.eventbrite.ie/e/the-dublin-city-market-day-free-ticket-tickets-1987382068265?utm_experiment=test_share_listing&amp;aff=ebdsshios&amp;utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAdGRleAROHBZleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA8xMjQwMjQ1NzQyODc0MTQAAae215-Yd-tqIFjbtXD_cUQT-4ccnrwqhSa4VhMIkBsaqlwQgYTxCjGrsmhrqg_aem_q3vfFqtT5Qm7CSto3yc7oA&amp;utm_id=97760_v0_s00_e0_tv3_a1denngz84ieda" xr:uid="{CF6F10C5-539E-49AA-83C8-AD9F39D80343}"/>
+    <hyperlink ref="M2" r:id="rId2" display="https://www.eventbrite.ie/e/_next/image?url=https%3A%2F%2Fimg.evbuc.com%2Fhttps%253A%252F%252Fcdn.evbuc.com%252Fimages%252F1182114598%252F2661084054671%252F1%252Foriginal.20260414-091433%3Fcrop%3Dfocalpoint%26fit%3Dcrop%26w%3D1880%26auto%3Dformat%252Ccompress%26q%3D75%26sharp%3D10%26fp-x%3D0.035%26fp-y%3D0.057%26s%3D99e443b6a1e707f2900fc8362638f8de&amp;w=1880&amp;q=75" xr:uid="{776602D2-A3ED-4967-B8DD-852A6E4B2EE5}"/>
+    <hyperlink ref="L3" r:id="rId3" location="location" xr:uid="{DFF3B79C-DF6D-437C-B16D-D0F1CC8C4202}"/>
+    <hyperlink ref="M3" r:id="rId4" display="https://www.eventbrite.ie/e/_next/image?url=https%3A%2F%2Fimg.evbuc.com%2Fhttps%253A%252F%252Fcdn.evbuc.com%252Fimages%252F1180032649%252F168066979823%252F1%252Foriginal.20260317-114958%3Fcrop%3Dfocalpoint%26fit%3Dcrop%26w%3D1880%26auto%3Dformat%252Ccompress%26q%3D75%26sharp%3D10%26fp-x%3D0.412%26fp-y%3D0.492%26s%3D9d6a3ea730dd98c09ab63fedc0eaecf0&amp;w=1880&amp;q=75" xr:uid="{DEFF551F-E1BC-42F2-9D66-7AC8002FE594}"/>
+    <hyperlink ref="L4" r:id="rId5" xr:uid="{6DC4ED09-3686-471C-ABAC-9B6741F9B9E9}"/>
+    <hyperlink ref="M4" r:id="rId6" xr:uid="{9EFC1056-2A16-4651-8620-1706CCD6D391}"/>
+    <hyperlink ref="L5" r:id="rId7" xr:uid="{C4A85081-A2C8-45B9-AE33-65E55A0F9A84}"/>
+    <hyperlink ref="M5" r:id="rId8" xr:uid="{3C0F9B81-1FA4-4C70-87B7-49EA34BFC97B}"/>
+    <hyperlink ref="M6" r:id="rId9" xr:uid="{B7E078E3-DBC7-4446-912E-68BF23CFBE38}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
